--- a/config/rules/CRS620MI.xlsx
+++ b/config/rules/CRS620MI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w10itasv\Documents\DevDataMigration\DevDataMigrationTool\GitHubDataMigration\DataMigrationTool\config\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB415032-D4F0-4947-897E-D4C8C08D1673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA98528-2939-49B5-A4F3-77881493711C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="_Audit_Log" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Rules!$A$1:$K$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Rules!$A$1:$K$135</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="477">
   <si>
     <t>TARGET_API</t>
   </si>
@@ -1522,6 +1522,9 @@
   </si>
   <si>
     <t>Override for WHS</t>
+  </si>
+  <si>
+    <t>SUNO#</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1893,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="8.88671875" customWidth="1"/>
@@ -4523,15 +4526,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>11</v>
       </c>
       <c r="B112" t="s">
-        <v>249</v>
+        <v>476</v>
       </c>
       <c r="C112" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="D112" t="s">
         <v>13</v>
@@ -4540,10 +4543,10 @@
         <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>250</v>
+        <v>124</v>
       </c>
       <c r="H112" t="s">
-        <v>251</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4551,10 +4554,10 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C113" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D113" t="s">
         <v>13</v>
@@ -4563,10 +4566,10 @@
         <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H113" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4574,10 +4577,10 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>126</v>
+        <v>252</v>
       </c>
       <c r="C114" t="s">
-        <v>126</v>
+        <v>252</v>
       </c>
       <c r="D114" t="s">
         <v>13</v>
@@ -4586,10 +4589,10 @@
         <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>127</v>
+        <v>253</v>
       </c>
       <c r="H114" t="s">
-        <v>128</v>
+        <v>254</v>
       </c>
     </row>
     <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4597,10 +4600,10 @@
         <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>338</v>
+        <v>126</v>
       </c>
       <c r="C115" t="s">
-        <v>338</v>
+        <v>126</v>
       </c>
       <c r="D115" t="s">
         <v>13</v>
@@ -4609,10 +4612,10 @@
         <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>339</v>
+        <v>127</v>
       </c>
       <c r="H115" t="s">
-        <v>340</v>
+        <v>128</v>
       </c>
     </row>
     <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4620,25 +4623,22 @@
         <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="C116" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="D116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E116" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="F116" t="s">
         <v>14</v>
       </c>
       <c r="G116" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="H116" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4646,22 +4646,25 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="C117" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="D117" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="E117" t="s">
+        <v>81</v>
       </c>
       <c r="F117" t="s">
         <v>14</v>
       </c>
       <c r="G117" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="H117" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
     </row>
     <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4669,10 +4672,10 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C118" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D118" t="s">
         <v>13</v>
@@ -4681,10 +4684,10 @@
         <v>14</v>
       </c>
       <c r="G118" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H118" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4692,22 +4695,22 @@
         <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="C119" t="s">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="D119" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F119" t="s">
         <v>14</v>
       </c>
       <c r="G119" t="s">
-        <v>217</v>
+        <v>290</v>
       </c>
       <c r="H119" t="s">
-        <v>218</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4715,22 +4718,22 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C120" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D120" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F120" t="s">
         <v>14</v>
       </c>
       <c r="G120" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="H120" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4738,10 +4741,10 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C121" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D121" t="s">
         <v>13</v>
@@ -4750,10 +4753,10 @@
         <v>14</v>
       </c>
       <c r="G121" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H121" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4761,25 +4764,22 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C122" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D122" t="s">
-        <v>18</v>
-      </c>
-      <c r="E122" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
       <c r="F122" t="s">
         <v>14</v>
       </c>
       <c r="G122" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H122" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4787,22 +4787,25 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C123" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="D123" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="E123" t="s">
+        <v>213</v>
       </c>
       <c r="F123" t="s">
         <v>14</v>
       </c>
       <c r="G123" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H123" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4810,10 +4813,10 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>129</v>
+        <v>196</v>
       </c>
       <c r="C124" t="s">
-        <v>129</v>
+        <v>196</v>
       </c>
       <c r="D124" t="s">
         <v>13</v>
@@ -4822,10 +4825,10 @@
         <v>14</v>
       </c>
       <c r="G124" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="H124" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
     </row>
     <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4833,10 +4836,10 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>308</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>308</v>
+        <v>129</v>
       </c>
       <c r="D125" t="s">
         <v>13</v>
@@ -4845,10 +4848,10 @@
         <v>14</v>
       </c>
       <c r="G125" t="s">
-        <v>309</v>
+        <v>130</v>
       </c>
       <c r="H125" t="s">
-        <v>310</v>
+        <v>131</v>
       </c>
     </row>
     <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4856,10 +4859,10 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C126" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D126" t="s">
         <v>13</v>
@@ -4868,10 +4871,10 @@
         <v>14</v>
       </c>
       <c r="G126" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H126" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4879,10 +4882,10 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="C127" t="s">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="D127" t="s">
         <v>13</v>
@@ -4891,10 +4894,10 @@
         <v>14</v>
       </c>
       <c r="G127" t="s">
-        <v>133</v>
+        <v>312</v>
       </c>
       <c r="H127" t="s">
-        <v>134</v>
+        <v>313</v>
       </c>
     </row>
     <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4902,10 +4905,10 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>429</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>429</v>
+        <v>132</v>
+      </c>
+      <c r="C128" t="s">
+        <v>132</v>
       </c>
       <c r="D128" t="s">
         <v>13</v>
@@ -4914,10 +4917,10 @@
         <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>448</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>410</v>
+        <v>133</v>
+      </c>
+      <c r="H128" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4925,25 +4928,22 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>189</v>
-      </c>
-      <c r="C129" t="s">
-        <v>189</v>
+        <v>429</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="D129" t="s">
         <v>13</v>
       </c>
-      <c r="E129" t="s">
-        <v>190</v>
-      </c>
       <c r="F129" t="s">
         <v>14</v>
       </c>
       <c r="G129" t="s">
-        <v>191</v>
-      </c>
-      <c r="H129" t="s">
-        <v>192</v>
+        <v>448</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4951,22 +4951,25 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>329</v>
+        <v>189</v>
       </c>
       <c r="C130" t="s">
-        <v>329</v>
+        <v>189</v>
       </c>
       <c r="D130" t="s">
         <v>13</v>
       </c>
+      <c r="E130" t="s">
+        <v>190</v>
+      </c>
       <c r="F130" t="s">
         <v>14</v>
       </c>
       <c r="G130" t="s">
-        <v>330</v>
+        <v>191</v>
       </c>
       <c r="H130" t="s">
-        <v>331</v>
+        <v>192</v>
       </c>
     </row>
     <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4974,10 +4977,10 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>329</v>
       </c>
       <c r="C131" t="s">
-        <v>135</v>
+        <v>329</v>
       </c>
       <c r="D131" t="s">
         <v>13</v>
@@ -4986,10 +4989,10 @@
         <v>14</v>
       </c>
       <c r="G131" t="s">
-        <v>136</v>
+        <v>330</v>
       </c>
       <c r="H131" t="s">
-        <v>137</v>
+        <v>331</v>
       </c>
     </row>
     <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -4997,10 +5000,10 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="C132" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="D132" t="s">
         <v>13</v>
@@ -5009,10 +5012,10 @@
         <v>14</v>
       </c>
       <c r="G132" t="s">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="H132" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -5020,10 +5023,10 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>305</v>
+        <v>186</v>
       </c>
       <c r="C133" t="s">
-        <v>305</v>
+        <v>186</v>
       </c>
       <c r="D133" t="s">
         <v>13</v>
@@ -5032,10 +5035,10 @@
         <v>14</v>
       </c>
       <c r="G133" t="s">
-        <v>306</v>
+        <v>187</v>
       </c>
       <c r="H133" t="s">
-        <v>307</v>
+        <v>188</v>
       </c>
     </row>
     <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -5043,48 +5046,45 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
+        <v>305</v>
+      </c>
+      <c r="C134" t="s">
+        <v>305</v>
+      </c>
+      <c r="D134" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
+        <v>306</v>
+      </c>
+      <c r="H134" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" t="s">
         <v>362</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C135" t="s">
         <v>362</v>
       </c>
-      <c r="D134" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" t="s">
-        <v>14</v>
-      </c>
-      <c r="G134" t="s">
+      <c r="D135" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135" t="s">
         <v>363</v>
       </c>
-      <c r="H134" t="s">
+      <c r="H135" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>11</v>
-      </c>
-      <c r="B135" t="s">
-        <v>456</v>
-      </c>
-      <c r="C135" t="s">
-        <v>21</v>
-      </c>
-      <c r="D135" t="s">
-        <v>457</v>
-      </c>
-      <c r="E135" t="s">
-        <v>464</v>
-      </c>
-      <c r="F135" t="s">
-        <v>458</v>
-      </c>
-      <c r="G135" t="s">
-        <v>470</v>
-      </c>
-      <c r="H135" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
@@ -5101,13 +5101,13 @@
         <v>457</v>
       </c>
       <c r="E136" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F136" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G136" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H136" t="s">
         <v>125</v>
@@ -5127,13 +5127,13 @@
         <v>457</v>
       </c>
       <c r="E137" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F137" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G137" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H137" t="s">
         <v>125</v>
@@ -5153,13 +5153,13 @@
         <v>457</v>
       </c>
       <c r="E138" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F138" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G138" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H138" t="s">
         <v>125</v>
@@ -5179,13 +5179,13 @@
         <v>457</v>
       </c>
       <c r="E139" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F139" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G139" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H139" t="s">
         <v>125</v>
@@ -5205,20 +5205,46 @@
         <v>457</v>
       </c>
       <c r="E140" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F140" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G140" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H140" t="s">
         <v>125</v>
       </c>
     </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" t="s">
+        <v>456</v>
+      </c>
+      <c r="C141" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" t="s">
+        <v>457</v>
+      </c>
+      <c r="E141" t="s">
+        <v>465</v>
+      </c>
+      <c r="F141" t="s">
+        <v>463</v>
+      </c>
+      <c r="G141" t="s">
+        <v>475</v>
+      </c>
+      <c r="H141" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K134" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:K135" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
         <filter val="SUNM"/>

--- a/config/rules/CRS620MI.xlsx
+++ b/config/rules/CRS620MI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w10itasv\Documents\DevDataMigration\DevDataMigrationTool\GitHubDataMigration\DataMigrationTool\config\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA98528-2939-49B5-A4F3-77881493711C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03419242-2676-4E80-82BD-790D86397937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="480">
   <si>
     <t>TARGET_API</t>
   </si>
@@ -1525,6 +1525,15 @@
   </si>
   <si>
     <t>SUNO#</t>
+  </si>
+  <si>
+    <t>STEM</t>
+  </si>
+  <si>
+    <t>ZZZZZZ</t>
+  </si>
+  <si>
+    <t>Mapped from STEM</t>
   </si>
 </sst>
 </file>
@@ -1892,8 +1901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K141"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="8.88671875" customWidth="1"/>
@@ -1936,7 +1944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1959,7 +1967,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1985,7 +1993,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2008,7 +2016,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2031,7 +2039,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2054,7 +2062,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2077,7 +2085,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2100,7 +2108,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2123,7 +2131,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2146,7 +2154,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2169,7 +2177,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2192,7 +2200,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2218,7 +2226,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2241,7 +2249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2267,7 +2275,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2290,7 +2298,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2313,7 +2321,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2336,7 +2344,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2382,7 +2390,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -2405,7 +2413,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -2428,7 +2436,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -2451,7 +2459,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2474,7 +2482,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -2497,7 +2505,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -2520,7 +2528,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -2543,7 +2551,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -2566,7 +2574,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -2589,7 +2597,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -2612,7 +2620,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -2638,7 +2646,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -2664,7 +2672,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -2690,7 +2698,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -2713,7 +2721,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -2736,7 +2744,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -2759,7 +2767,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -2782,7 +2790,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -2805,7 +2813,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -2831,7 +2839,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -2857,7 +2865,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -2883,7 +2891,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -2906,7 +2914,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -2929,7 +2937,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -2955,7 +2963,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -2978,7 +2986,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -3001,7 +3009,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -3024,7 +3032,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -3047,7 +3055,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -3070,7 +3078,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -3093,7 +3101,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -3119,7 +3127,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -3142,7 +3150,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -3165,7 +3173,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -3188,7 +3196,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -3211,7 +3219,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -3234,7 +3242,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -3260,7 +3268,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -3286,7 +3294,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -3312,7 +3320,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -3338,7 +3346,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -3361,7 +3369,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -3384,7 +3392,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -3410,7 +3418,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -3433,7 +3441,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -3459,7 +3467,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -3482,7 +3490,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -3505,7 +3513,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -3528,7 +3536,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -3551,7 +3559,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -3574,7 +3582,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -3597,7 +3605,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -3620,7 +3628,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -3643,7 +3651,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -3666,7 +3674,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -3689,7 +3697,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -3712,7 +3720,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -3735,7 +3743,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -3758,7 +3766,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -3781,7 +3789,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -3804,7 +3812,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -3827,7 +3835,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -3850,7 +3858,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -3873,7 +3881,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -3896,7 +3904,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -3919,7 +3927,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -3942,7 +3950,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -3965,7 +3973,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -3988,7 +3996,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -4011,7 +4019,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -4034,7 +4042,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -4057,7 +4065,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -4080,7 +4088,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -4103,7 +4111,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -4126,7 +4134,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -4149,7 +4157,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -4172,7 +4180,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -4195,7 +4203,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -4221,7 +4229,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -4247,7 +4255,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -4270,7 +4278,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -4293,7 +4301,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -4316,7 +4324,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -4339,7 +4347,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -4362,7 +4370,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -4385,7 +4393,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -4408,7 +4416,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -4431,7 +4439,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -4454,7 +4462,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -4549,7 +4557,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -4572,7 +4580,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -4595,7 +4603,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -4618,7 +4626,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -4641,7 +4649,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -4667,7 +4675,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -4690,7 +4698,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -4713,7 +4721,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -4736,7 +4744,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -4759,7 +4767,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -4782,7 +4790,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -4808,7 +4816,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -4831,7 +4839,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -4854,7 +4862,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -4877,7 +4885,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -4900,7 +4908,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -4923,7 +4931,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -4946,7 +4954,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -4972,7 +4980,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>11</v>
       </c>
@@ -4995,7 +5003,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>11</v>
       </c>
@@ -5018,7 +5026,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>11</v>
       </c>
@@ -5041,7 +5049,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>11</v>
       </c>
@@ -5064,7 +5072,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>11</v>
       </c>
@@ -5243,15 +5251,34 @@
         <v>125</v>
       </c>
     </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142" t="s">
+        <v>477</v>
+      </c>
+      <c r="C142" t="s">
+        <v>477</v>
+      </c>
+      <c r="D142" t="s">
+        <v>18</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F142" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" t="s">
+        <v>479</v>
+      </c>
+      <c r="H142" t="s">
+        <v>479</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K135" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="SUNM"/>
-        <filter val="SUNO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K135" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
